--- a/Data/g13.1b.xlsx
+++ b/Data/g13.1b.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,16 +453,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tocantins</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.17</v>
+        <v>2.83</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,16 +473,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -493,16 +493,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rondônia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -518,11 +518,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.95</v>
+        <v>1.13</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -533,16 +533,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Roraima</t>
+          <t>Sergipe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -553,12 +553,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Paraíba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -573,54 +573,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>26º</t>
-        </is>
-      </c>
+        <v>-0.02</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diferença 2025/04 - 2024/04</t>
+          <t>Diferença 2026/04 - 2025/04</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.41</v>
+        <v>-0.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nordeste</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Diferença 2025/04 - 2024/04</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
